--- a/تقرير_المبيعات_والمخزن_مقسم_معدل.xlsx
+++ b/تقرير_المبيعات_والمخزن_مقسم_معدل.xlsx
@@ -806,7 +806,7 @@
         <v>106</v>
       </c>
       <c r="E14">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F14">
         <v>76</v>
@@ -818,7 +818,7 @@
         <v>76</v>
       </c>
       <c r="I14">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15">
@@ -835,7 +835,7 @@
         <v>107</v>
       </c>
       <c r="E15">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F15">
         <v>60</v>
@@ -847,7 +847,7 @@
         <v>60</v>
       </c>
       <c r="I15">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16">
@@ -864,7 +864,7 @@
         <v>108</v>
       </c>
       <c r="E16">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F16">
         <v>68</v>
@@ -876,7 +876,7 @@
         <v>68</v>
       </c>
       <c r="I16">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17">
@@ -1038,7 +1038,7 @@
         <v>96</v>
       </c>
       <c r="E22">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="F22">
         <v>52</v>
@@ -1050,7 +1050,7 @@
         <v>52</v>
       </c>
       <c r="I22">
-        <v>136</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23">
@@ -1154,16 +1154,16 @@
         <v>148</v>
       </c>
       <c r="E26">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F26">
         <v>152</v>
       </c>
       <c r="G26">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H26">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1183,16 +1183,16 @@
         <v>149</v>
       </c>
       <c r="E27">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F27">
         <v>136</v>
       </c>
       <c r="G27">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H27">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1241,7 +1241,7 @@
         <v>151</v>
       </c>
       <c r="E29">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F29">
         <v>180</v>
@@ -1253,7 +1253,7 @@
         <v>180</v>
       </c>
       <c r="I29">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -2082,7 +2082,7 @@
         <v>76</v>
       </c>
       <c r="E58">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="F58">
         <v>204</v>
@@ -2094,7 +2094,7 @@
         <v>204</v>
       </c>
       <c r="I58">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
@@ -2111,19 +2111,19 @@
         <v>77</v>
       </c>
       <c r="E59">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="F59">
         <v>200</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I59">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2140,16 +2140,16 @@
         <v>78</v>
       </c>
       <c r="E60">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F60">
         <v>184</v>
       </c>
       <c r="G60">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="H60">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -2343,7 +2343,7 @@
         <v>159</v>
       </c>
       <c r="E67">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F67">
         <v>116</v>
@@ -2355,7 +2355,7 @@
         <v>116</v>
       </c>
       <c r="I67">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68">
@@ -2372,16 +2372,16 @@
         <v>160</v>
       </c>
       <c r="E68">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="F68">
         <v>228</v>
       </c>
       <c r="G68">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="H68">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -2401,19 +2401,19 @@
         <v>161</v>
       </c>
       <c r="E69">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="F69">
         <v>204</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H69">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="I69">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2430,7 +2430,7 @@
         <v>112</v>
       </c>
       <c r="E70">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F70">
         <v>144</v>
@@ -2442,7 +2442,7 @@
         <v>144</v>
       </c>
       <c r="I70">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="71">
@@ -2459,7 +2459,7 @@
         <v>113</v>
       </c>
       <c r="E71">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F71">
         <v>148</v>
@@ -2471,7 +2471,7 @@
         <v>148</v>
       </c>
       <c r="I71">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="72">
@@ -2488,7 +2488,7 @@
         <v>114</v>
       </c>
       <c r="E72">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F72">
         <v>84</v>
@@ -2500,7 +2500,7 @@
         <v>84</v>
       </c>
       <c r="I72">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="73">
@@ -2517,7 +2517,7 @@
         <v>103</v>
       </c>
       <c r="E73">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F73">
         <v>52</v>
@@ -2529,7 +2529,7 @@
         <v>52</v>
       </c>
       <c r="I73">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="74">
@@ -2575,7 +2575,7 @@
         <v>105</v>
       </c>
       <c r="E75">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F75">
         <v>64</v>
@@ -2587,7 +2587,7 @@
         <v>64</v>
       </c>
       <c r="I75">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="76">
@@ -2662,7 +2662,7 @@
         <v>144</v>
       </c>
       <c r="E78">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="F78">
         <v>100</v>
@@ -2674,7 +2674,7 @@
         <v>100</v>
       </c>
       <c r="I78">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="79">
@@ -2691,16 +2691,16 @@
         <v>185</v>
       </c>
       <c r="E79">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F79">
         <v>244</v>
       </c>
       <c r="G79">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H79">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -2720,7 +2720,7 @@
         <v>186</v>
       </c>
       <c r="E80">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="F80">
         <v>176</v>
@@ -2732,7 +2732,7 @@
         <v>176</v>
       </c>
       <c r="I80">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81">
@@ -2749,7 +2749,7 @@
         <v>187</v>
       </c>
       <c r="E81">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F81">
         <v>164</v>
@@ -2761,7 +2761,7 @@
         <v>164</v>
       </c>
       <c r="I81">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="82">
@@ -2778,7 +2778,7 @@
         <v>197</v>
       </c>
       <c r="E82">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F82">
         <v>68</v>
@@ -2790,7 +2790,7 @@
         <v>68</v>
       </c>
       <c r="I82">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="83">
@@ -2807,7 +2807,7 @@
         <v>198</v>
       </c>
       <c r="E83">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F83">
         <v>88</v>
@@ -2819,7 +2819,7 @@
         <v>88</v>
       </c>
       <c r="I83">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="84">
@@ -2836,7 +2836,7 @@
         <v>199</v>
       </c>
       <c r="E84">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F84">
         <v>64</v>
@@ -2848,7 +2848,7 @@
         <v>64</v>
       </c>
       <c r="I84">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="85">
@@ -2865,7 +2865,7 @@
         <v>194</v>
       </c>
       <c r="E85">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F85">
         <v>132</v>
@@ -2877,7 +2877,7 @@
         <v>132</v>
       </c>
       <c r="I85">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="86">
@@ -2894,7 +2894,7 @@
         <v>195</v>
       </c>
       <c r="E86">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F86">
         <v>124</v>
@@ -2906,7 +2906,7 @@
         <v>124</v>
       </c>
       <c r="I86">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="87">
@@ -2923,7 +2923,7 @@
         <v>196</v>
       </c>
       <c r="E87">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F87">
         <v>120</v>
@@ -2935,7 +2935,7 @@
         <v>120</v>
       </c>
       <c r="I87">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="88">
@@ -2952,7 +2952,7 @@
         <v>200</v>
       </c>
       <c r="E88">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="F88">
         <v>156</v>
@@ -2964,7 +2964,7 @@
         <v>156</v>
       </c>
       <c r="I88">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="89">
@@ -2981,16 +2981,16 @@
         <v>201</v>
       </c>
       <c r="E89">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F89">
         <v>196</v>
       </c>
       <c r="G89">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H89">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -3039,16 +3039,16 @@
         <v>305</v>
       </c>
       <c r="E91">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F91">
         <v>200</v>
       </c>
       <c r="G91">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H91">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -3068,16 +3068,16 @@
         <v>306</v>
       </c>
       <c r="E92">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F92">
         <v>144</v>
       </c>
       <c r="G92">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H92">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -3097,16 +3097,16 @@
         <v>307</v>
       </c>
       <c r="E93">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F93">
         <v>104</v>
       </c>
       <c r="G93">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H93">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -3126,7 +3126,7 @@
         <v>308</v>
       </c>
       <c r="E94">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F94">
         <v>80</v>
@@ -3138,7 +3138,7 @@
         <v>80</v>
       </c>
       <c r="I94">
-        <v>67</v>
+        <v>48</v>
       </c>
     </row>
     <row r="95">
@@ -3184,7 +3184,7 @@
         <v>310</v>
       </c>
       <c r="E96">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="F96">
         <v>60</v>
@@ -3196,7 +3196,7 @@
         <v>60</v>
       </c>
       <c r="I96">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="97">
@@ -3213,7 +3213,7 @@
         <v>311</v>
       </c>
       <c r="E97">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="F97">
         <v>56</v>
@@ -3225,7 +3225,7 @@
         <v>56</v>
       </c>
       <c r="I97">
-        <v>73</v>
+        <v>60</v>
       </c>
     </row>
     <row r="98">
@@ -3242,16 +3242,16 @@
         <v>312</v>
       </c>
       <c r="E98">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F98">
         <v>224</v>
       </c>
       <c r="G98">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H98">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -3271,16 +3271,16 @@
         <v>313</v>
       </c>
       <c r="E99">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F99">
         <v>304</v>
       </c>
       <c r="G99">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="H99">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -3300,16 +3300,16 @@
         <v>314</v>
       </c>
       <c r="E100">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F100">
         <v>208</v>
       </c>
       <c r="G100">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H100">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -3358,16 +3358,16 @@
         <v>316</v>
       </c>
       <c r="E102">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F102">
         <v>216</v>
       </c>
       <c r="G102">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H102">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I102">
         <v>0</v>
@@ -3387,16 +3387,16 @@
         <v>317</v>
       </c>
       <c r="E103">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F103">
         <v>204</v>
       </c>
       <c r="G103">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="H103">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I103">
         <v>0</v>
@@ -3416,16 +3416,16 @@
         <v>318</v>
       </c>
       <c r="E104">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F104">
         <v>164</v>
       </c>
       <c r="G104">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="H104">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I104">
         <v>0</v>
@@ -3445,16 +3445,16 @@
         <v>319</v>
       </c>
       <c r="E105">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F105">
         <v>148</v>
       </c>
       <c r="G105">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="H105">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -3503,16 +3503,16 @@
         <v>321</v>
       </c>
       <c r="E107">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F107">
         <v>176</v>
       </c>
       <c r="G107">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="H107">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I107">
         <v>0</v>
@@ -3532,16 +3532,16 @@
         <v>322</v>
       </c>
       <c r="E108">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F108">
         <v>124</v>
       </c>
       <c r="G108">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="H108">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -3561,16 +3561,16 @@
         <v>323</v>
       </c>
       <c r="E109">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F109">
         <v>184</v>
       </c>
       <c r="G109">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="H109">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I109">
         <v>0</v>
@@ -3677,16 +3677,16 @@
         <v>327</v>
       </c>
       <c r="E113">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F113">
         <v>100</v>
       </c>
       <c r="G113">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H113">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I113">
         <v>0</v>
@@ -3764,16 +3764,16 @@
         <v>330</v>
       </c>
       <c r="E116">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F116">
         <v>72</v>
       </c>
       <c r="G116">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="H116">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I116">
         <v>0</v>
@@ -3793,16 +3793,16 @@
         <v>331</v>
       </c>
       <c r="E117">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F117">
         <v>84</v>
       </c>
       <c r="G117">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H117">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I117">
         <v>0</v>
@@ -3822,16 +3822,16 @@
         <v>332</v>
       </c>
       <c r="E118">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F118">
         <v>108</v>
       </c>
       <c r="G118">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="H118">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I118">
         <v>0</v>
@@ -3851,16 +3851,16 @@
         <v>547</v>
       </c>
       <c r="E119">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F119">
         <v>72</v>
       </c>
       <c r="G119">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H119">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I119">
         <v>0</v>
@@ -3880,16 +3880,16 @@
         <v>548</v>
       </c>
       <c r="E120">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F120">
         <v>64</v>
       </c>
       <c r="G120">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H120">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I120">
         <v>0</v>
@@ -3909,16 +3909,16 @@
         <v>549</v>
       </c>
       <c r="E121">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F121">
         <v>76</v>
       </c>
       <c r="G121">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H121">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I121">
         <v>0</v>
@@ -4054,7 +4054,7 @@
         <v>85</v>
       </c>
       <c r="E126">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F126">
         <v>148</v>
@@ -4066,7 +4066,7 @@
         <v>148</v>
       </c>
       <c r="I126">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="127">
@@ -4083,7 +4083,7 @@
         <v>86</v>
       </c>
       <c r="E127">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="F127">
         <v>128</v>
@@ -4095,7 +4095,7 @@
         <v>128</v>
       </c>
       <c r="I127">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="128">
@@ -4112,7 +4112,7 @@
         <v>87</v>
       </c>
       <c r="E128">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F128">
         <v>84</v>
@@ -4124,7 +4124,7 @@
         <v>84</v>
       </c>
       <c r="I128">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="129">
@@ -4315,7 +4315,7 @@
         <v>230</v>
       </c>
       <c r="E135">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F135">
         <v>60</v>
@@ -4327,7 +4327,7 @@
         <v>60</v>
       </c>
       <c r="I135">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="136">
@@ -4402,7 +4402,7 @@
         <v>115</v>
       </c>
       <c r="E138">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F138">
         <v>48</v>
@@ -4414,7 +4414,7 @@
         <v>48</v>
       </c>
       <c r="I138">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="139">
@@ -4460,7 +4460,7 @@
         <v>117</v>
       </c>
       <c r="E140">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F140">
         <v>64</v>
@@ -4472,7 +4472,7 @@
         <v>64</v>
       </c>
       <c r="I140">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="141">
@@ -4576,7 +4576,7 @@
         <v>145</v>
       </c>
       <c r="E144">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="F144">
         <v>124</v>
@@ -4588,7 +4588,7 @@
         <v>124</v>
       </c>
       <c r="I144">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="145">
@@ -4634,7 +4634,7 @@
         <v>147</v>
       </c>
       <c r="E146">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F146">
         <v>132</v>
@@ -4646,7 +4646,7 @@
         <v>132</v>
       </c>
       <c r="I146">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="147">
@@ -4663,7 +4663,7 @@
         <v>182</v>
       </c>
       <c r="E147">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F147">
         <v>172</v>
@@ -4675,7 +4675,7 @@
         <v>172</v>
       </c>
       <c r="I147">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="148">
@@ -4750,7 +4750,7 @@
         <v>203</v>
       </c>
       <c r="E150">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F150">
         <v>52</v>
@@ -4762,7 +4762,7 @@
         <v>52</v>
       </c>
       <c r="I150">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="151">
@@ -4837,7 +4837,7 @@
         <v>206</v>
       </c>
       <c r="E153">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F153">
         <v>92</v>
@@ -4849,7 +4849,7 @@
         <v>92</v>
       </c>
       <c r="I153">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="154">
@@ -4924,7 +4924,7 @@
         <v>209</v>
       </c>
       <c r="E156">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="F156">
         <v>156</v>
@@ -4936,7 +4936,7 @@
         <v>156</v>
       </c>
       <c r="I156">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="157">
@@ -5098,7 +5098,7 @@
         <v>336</v>
       </c>
       <c r="E162">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F162">
         <v>92</v>
@@ -5110,7 +5110,7 @@
         <v>92</v>
       </c>
       <c r="I162">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="163">
@@ -5127,7 +5127,7 @@
         <v>337</v>
       </c>
       <c r="E163">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="F163">
         <v>104</v>
@@ -5139,7 +5139,7 @@
         <v>104</v>
       </c>
       <c r="I163">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="164">
@@ -5156,7 +5156,7 @@
         <v>338</v>
       </c>
       <c r="E164">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F164">
         <v>132</v>
@@ -5168,7 +5168,7 @@
         <v>132</v>
       </c>
       <c r="I164">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="165">
@@ -5185,16 +5185,16 @@
         <v>339</v>
       </c>
       <c r="E165">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F165">
         <v>272</v>
       </c>
       <c r="G165">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="H165">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I165">
         <v>0</v>
@@ -5243,16 +5243,16 @@
         <v>341</v>
       </c>
       <c r="E167">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F167">
         <v>272</v>
       </c>
       <c r="G167">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="H167">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I167">
         <v>0</v>
@@ -5272,16 +5272,16 @@
         <v>342</v>
       </c>
       <c r="E168">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F168">
         <v>216</v>
       </c>
       <c r="G168">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H168">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I168">
         <v>0</v>
@@ -5330,16 +5330,16 @@
         <v>344</v>
       </c>
       <c r="E170">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F170">
         <v>224</v>
       </c>
       <c r="G170">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="H170">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I170">
         <v>0</v>
@@ -5359,16 +5359,16 @@
         <v>345</v>
       </c>
       <c r="E171">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F171">
         <v>100</v>
       </c>
       <c r="G171">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H171">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I171">
         <v>0</v>
@@ -5388,16 +5388,16 @@
         <v>346</v>
       </c>
       <c r="E172">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F172">
         <v>132</v>
       </c>
       <c r="G172">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H172">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I172">
         <v>0</v>
@@ -5417,16 +5417,16 @@
         <v>347</v>
       </c>
       <c r="E173">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F173">
         <v>120</v>
       </c>
       <c r="G173">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H173">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I173">
         <v>0</v>
@@ -5446,16 +5446,16 @@
         <v>351</v>
       </c>
       <c r="E174">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F174">
         <v>140</v>
       </c>
       <c r="G174">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H174">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I174">
         <v>0</v>
@@ -5504,16 +5504,16 @@
         <v>353</v>
       </c>
       <c r="E176">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F176">
         <v>176</v>
       </c>
       <c r="G176">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="H176">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I176">
         <v>0</v>
@@ -5707,16 +5707,16 @@
         <v>357</v>
       </c>
       <c r="E183">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F183">
         <v>132</v>
       </c>
       <c r="G183">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H183">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I183">
         <v>0</v>
@@ -5736,16 +5736,16 @@
         <v>358</v>
       </c>
       <c r="E184">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F184">
         <v>136</v>
       </c>
       <c r="G184">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H184">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I184">
         <v>0</v>
@@ -5765,16 +5765,16 @@
         <v>359</v>
       </c>
       <c r="E185">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F185">
         <v>152</v>
       </c>
       <c r="G185">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H185">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I185">
         <v>0</v>
@@ -5968,7 +5968,7 @@
         <v>67</v>
       </c>
       <c r="E192">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F192">
         <v>148</v>
@@ -5980,7 +5980,7 @@
         <v>148</v>
       </c>
       <c r="I192">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="193">
@@ -5997,7 +5997,7 @@
         <v>68</v>
       </c>
       <c r="E193">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F193">
         <v>188</v>
@@ -6009,7 +6009,7 @@
         <v>188</v>
       </c>
       <c r="I193">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="194">
@@ -6026,7 +6026,7 @@
         <v>69</v>
       </c>
       <c r="E194">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F194">
         <v>136</v>
@@ -6038,7 +6038,7 @@
         <v>136</v>
       </c>
       <c r="I194">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="195">
@@ -6055,7 +6055,7 @@
         <v>70</v>
       </c>
       <c r="E195">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F195">
         <v>148</v>
@@ -6067,7 +6067,7 @@
         <v>148</v>
       </c>
       <c r="I195">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="196">
@@ -6084,7 +6084,7 @@
         <v>71</v>
       </c>
       <c r="E196">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F196">
         <v>160</v>
@@ -6096,7 +6096,7 @@
         <v>160</v>
       </c>
       <c r="I196">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="197">
@@ -6142,7 +6142,7 @@
         <v>73</v>
       </c>
       <c r="E198">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F198">
         <v>108</v>
@@ -6154,7 +6154,7 @@
         <v>108</v>
       </c>
       <c r="I198">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="199">
@@ -6171,7 +6171,7 @@
         <v>74</v>
       </c>
       <c r="E199">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F199">
         <v>96</v>
@@ -6183,7 +6183,7 @@
         <v>96</v>
       </c>
       <c r="I199">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="200">
@@ -6519,7 +6519,7 @@
         <v>179</v>
       </c>
       <c r="E211">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F211">
         <v>136</v>
@@ -6531,7 +6531,7 @@
         <v>136</v>
       </c>
       <c r="I211">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="212">
@@ -6548,16 +6548,16 @@
         <v>180</v>
       </c>
       <c r="E212">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F212">
         <v>136</v>
       </c>
       <c r="G212">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H212">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I212">
         <v>0</v>
@@ -6577,16 +6577,16 @@
         <v>181</v>
       </c>
       <c r="E213">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F213">
         <v>100</v>
       </c>
       <c r="G213">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H213">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I213">
         <v>0</v>
@@ -6606,7 +6606,7 @@
         <v>212</v>
       </c>
       <c r="E214">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F214">
         <v>80</v>
@@ -6618,7 +6618,7 @@
         <v>80</v>
       </c>
       <c r="I214">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="215">
@@ -6693,7 +6693,7 @@
         <v>215</v>
       </c>
       <c r="E217">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F217">
         <v>40</v>
@@ -6705,7 +6705,7 @@
         <v>40</v>
       </c>
       <c r="I217">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="218">
@@ -7041,16 +7041,16 @@
         <v>281</v>
       </c>
       <c r="E229">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F229">
         <v>168</v>
       </c>
       <c r="G229">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H229">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I229">
         <v>0</v>
@@ -7070,16 +7070,16 @@
         <v>282</v>
       </c>
       <c r="E230">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F230">
         <v>236</v>
       </c>
       <c r="G230">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="H230">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I230">
         <v>0</v>
@@ -7099,16 +7099,16 @@
         <v>283</v>
       </c>
       <c r="E231">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F231">
         <v>212</v>
       </c>
       <c r="G231">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H231">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I231">
         <v>0</v>
@@ -7215,16 +7215,16 @@
         <v>556</v>
       </c>
       <c r="E235">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F235">
         <v>144</v>
       </c>
       <c r="G235">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H235">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I235">
         <v>0</v>
@@ -7244,16 +7244,16 @@
         <v>557</v>
       </c>
       <c r="E236">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F236">
         <v>260</v>
       </c>
       <c r="G236">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="H236">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I236">
         <v>0</v>
@@ -7505,7 +7505,7 @@
         <v>12</v>
       </c>
       <c r="E245">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="F245">
         <v>112</v>
@@ -7517,7 +7517,7 @@
         <v>112</v>
       </c>
       <c r="I245">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="246">
@@ -7534,7 +7534,7 @@
         <v>13</v>
       </c>
       <c r="E246">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F246">
         <v>152</v>
@@ -7546,7 +7546,7 @@
         <v>152</v>
       </c>
       <c r="I246">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="247">
@@ -7563,7 +7563,7 @@
         <v>14</v>
       </c>
       <c r="E247">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="F247">
         <v>92</v>
@@ -7575,7 +7575,7 @@
         <v>92</v>
       </c>
       <c r="I247">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="248">
@@ -7621,7 +7621,7 @@
         <v>41</v>
       </c>
       <c r="E249">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="F249">
         <v>172</v>
@@ -7633,7 +7633,7 @@
         <v>172</v>
       </c>
       <c r="I249">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="250">
@@ -7650,7 +7650,7 @@
         <v>42</v>
       </c>
       <c r="E250">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="F250">
         <v>136</v>
@@ -7662,7 +7662,7 @@
         <v>136</v>
       </c>
       <c r="I250">
-        <v>73</v>
+        <v>63</v>
       </c>
     </row>
     <row r="251">
@@ -7679,16 +7679,16 @@
         <v>55</v>
       </c>
       <c r="E251">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F251">
         <v>212</v>
       </c>
       <c r="G251">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H251">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="I251">
         <v>0</v>
@@ -7824,7 +7824,7 @@
         <v>54</v>
       </c>
       <c r="E256">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="F256">
         <v>108</v>
@@ -7836,7 +7836,7 @@
         <v>108</v>
       </c>
       <c r="I256">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="257">
@@ -7853,16 +7853,16 @@
         <v>124</v>
       </c>
       <c r="E257">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F257">
         <v>276</v>
       </c>
       <c r="G257">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H257">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I257">
         <v>0</v>
@@ -7911,16 +7911,16 @@
         <v>126</v>
       </c>
       <c r="E259">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F259">
         <v>248</v>
       </c>
       <c r="G259">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="H259">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I259">
         <v>0</v>
@@ -8027,7 +8027,7 @@
         <v>136</v>
       </c>
       <c r="E263">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F263">
         <v>104</v>
@@ -8039,7 +8039,7 @@
         <v>104</v>
       </c>
       <c r="I263">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="264">
@@ -8056,7 +8056,7 @@
         <v>137</v>
       </c>
       <c r="E264">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F264">
         <v>152</v>
@@ -8068,7 +8068,7 @@
         <v>152</v>
       </c>
       <c r="I264">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="265">
@@ -8085,7 +8085,7 @@
         <v>138</v>
       </c>
       <c r="E265">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F265">
         <v>104</v>
@@ -8097,7 +8097,7 @@
         <v>104</v>
       </c>
       <c r="I265">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="266">
@@ -8114,16 +8114,16 @@
         <v>139</v>
       </c>
       <c r="E266">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="F266">
         <v>228</v>
       </c>
       <c r="G266">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H266">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="I266">
         <v>0</v>
@@ -8143,7 +8143,7 @@
         <v>140</v>
       </c>
       <c r="E267">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F267">
         <v>140</v>
@@ -8155,7 +8155,7 @@
         <v>140</v>
       </c>
       <c r="I267">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="268">
@@ -8172,7 +8172,7 @@
         <v>141</v>
       </c>
       <c r="E268">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="F268">
         <v>172</v>
@@ -8184,7 +8184,7 @@
         <v>172</v>
       </c>
       <c r="I268">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="269">
@@ -8201,16 +8201,16 @@
         <v>169</v>
       </c>
       <c r="E269">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F269">
         <v>216</v>
       </c>
       <c r="G269">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H269">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I269">
         <v>0</v>
@@ -8259,16 +8259,16 @@
         <v>171</v>
       </c>
       <c r="E271">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F271">
         <v>204</v>
       </c>
       <c r="G271">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H271">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I271">
         <v>0</v>
@@ -8288,7 +8288,7 @@
         <v>218</v>
       </c>
       <c r="E272">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="F272">
         <v>168</v>
@@ -8300,7 +8300,7 @@
         <v>168</v>
       </c>
       <c r="I272">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="273">
@@ -8317,7 +8317,7 @@
         <v>219</v>
       </c>
       <c r="E273">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="F273">
         <v>172</v>
@@ -8329,7 +8329,7 @@
         <v>172</v>
       </c>
       <c r="I273">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="274">
@@ -8346,7 +8346,7 @@
         <v>220</v>
       </c>
       <c r="E274">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="F274">
         <v>100</v>
@@ -8358,7 +8358,7 @@
         <v>100</v>
       </c>
       <c r="I274">
-        <v>74</v>
+        <v>64</v>
       </c>
     </row>
     <row r="275">
@@ -8375,7 +8375,7 @@
         <v>221</v>
       </c>
       <c r="E275">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F275">
         <v>56</v>
@@ -8387,7 +8387,7 @@
         <v>56</v>
       </c>
       <c r="I275">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="276">
@@ -8404,7 +8404,7 @@
         <v>222</v>
       </c>
       <c r="E276">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F276">
         <v>124</v>
@@ -8416,7 +8416,7 @@
         <v>124</v>
       </c>
       <c r="I276">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="277">
@@ -8462,16 +8462,16 @@
         <v>248</v>
       </c>
       <c r="E278">
-        <v>358</v>
+        <v>172</v>
       </c>
       <c r="F278">
         <v>372</v>
       </c>
       <c r="G278">
-        <v>14</v>
+        <v>200</v>
       </c>
       <c r="H278">
-        <v>358</v>
+        <v>172</v>
       </c>
       <c r="I278">
         <v>0</v>
@@ -8491,16 +8491,16 @@
         <v>249</v>
       </c>
       <c r="E279">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="F279">
         <v>228</v>
       </c>
       <c r="G279">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H279">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="I279">
         <v>0</v>
@@ -8520,16 +8520,16 @@
         <v>250</v>
       </c>
       <c r="E280">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="F280">
         <v>368</v>
       </c>
       <c r="G280">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="H280">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="I280">
         <v>0</v>
@@ -8549,7 +8549,7 @@
         <v>251</v>
       </c>
       <c r="E281">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F281">
         <v>52</v>
@@ -8561,7 +8561,7 @@
         <v>52</v>
       </c>
       <c r="I281">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="282">
@@ -8578,7 +8578,7 @@
         <v>252</v>
       </c>
       <c r="E282">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F282">
         <v>52</v>
@@ -8590,7 +8590,7 @@
         <v>52</v>
       </c>
       <c r="I282">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="283">
@@ -8607,7 +8607,7 @@
         <v>253</v>
       </c>
       <c r="E283">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F283">
         <v>68</v>
@@ -8619,7 +8619,7 @@
         <v>68</v>
       </c>
       <c r="I283">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="284">
@@ -8665,16 +8665,16 @@
         <v>255</v>
       </c>
       <c r="E285">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F285">
         <v>160</v>
       </c>
       <c r="G285">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="H285">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I285">
         <v>0</v>
@@ -8694,16 +8694,16 @@
         <v>256</v>
       </c>
       <c r="E286">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F286">
         <v>108</v>
       </c>
       <c r="G286">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H286">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I286">
         <v>0</v>
@@ -8897,16 +8897,16 @@
         <v>293</v>
       </c>
       <c r="E293">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F293">
         <v>172</v>
       </c>
       <c r="G293">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="H293">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I293">
         <v>0</v>
@@ -8955,16 +8955,16 @@
         <v>295</v>
       </c>
       <c r="E295">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F295">
         <v>196</v>
       </c>
       <c r="G295">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="H295">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I295">
         <v>0</v>
@@ -8984,16 +8984,16 @@
         <v>296</v>
       </c>
       <c r="E296">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F296">
         <v>192</v>
       </c>
       <c r="G296">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="H296">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I296">
         <v>0</v>
@@ -9013,16 +9013,16 @@
         <v>297</v>
       </c>
       <c r="E297">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F297">
         <v>132</v>
       </c>
       <c r="G297">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H297">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I297">
         <v>0</v>
@@ -9042,16 +9042,16 @@
         <v>298</v>
       </c>
       <c r="E298">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F298">
         <v>192</v>
       </c>
       <c r="G298">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="H298">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I298">
         <v>0</v>
@@ -9158,16 +9158,16 @@
         <v>565</v>
       </c>
       <c r="E302">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F302">
         <v>140</v>
       </c>
       <c r="G302">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H302">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I302">
         <v>0</v>
@@ -9187,16 +9187,16 @@
         <v>566</v>
       </c>
       <c r="E303">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F303">
         <v>220</v>
       </c>
       <c r="G303">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H303">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I303">
         <v>0</v>
@@ -9216,16 +9216,16 @@
         <v>567</v>
       </c>
       <c r="E304">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F304">
         <v>192</v>
       </c>
       <c r="G304">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H304">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I304">
         <v>0</v>
@@ -9419,16 +9419,16 @@
         <v>18</v>
       </c>
       <c r="E311">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F311">
         <v>212</v>
       </c>
       <c r="G311">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="H311">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="I311">
         <v>0</v>
@@ -10173,7 +10173,7 @@
         <v>166</v>
       </c>
       <c r="E337">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F337">
         <v>56</v>
@@ -10185,7 +10185,7 @@
         <v>56</v>
       </c>
       <c r="I337">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="338">
@@ -10231,7 +10231,7 @@
         <v>168</v>
       </c>
       <c r="E339">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F339">
         <v>120</v>
@@ -10243,7 +10243,7 @@
         <v>120</v>
       </c>
       <c r="I339">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="340">
@@ -10289,16 +10289,16 @@
         <v>225</v>
       </c>
       <c r="E341">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F341">
         <v>112</v>
       </c>
       <c r="G341">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H341">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I341">
         <v>0</v>
@@ -10318,7 +10318,7 @@
         <v>226</v>
       </c>
       <c r="E342">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F342">
         <v>164</v>
@@ -10330,7 +10330,7 @@
         <v>164</v>
       </c>
       <c r="I342">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="343">
@@ -10347,7 +10347,7 @@
         <v>227</v>
       </c>
       <c r="E343">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F343">
         <v>68</v>
@@ -10359,7 +10359,7 @@
         <v>68</v>
       </c>
       <c r="I343">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="344">
@@ -10405,7 +10405,7 @@
         <v>229</v>
       </c>
       <c r="E345">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F345">
         <v>120</v>
@@ -10417,7 +10417,7 @@
         <v>120</v>
       </c>
       <c r="I345">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="346">
@@ -10434,16 +10434,16 @@
         <v>260</v>
       </c>
       <c r="E346">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="F346">
         <v>324</v>
       </c>
       <c r="G346">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H346">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="I346">
         <v>0</v>
@@ -10463,16 +10463,16 @@
         <v>261</v>
       </c>
       <c r="E347">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="F347">
         <v>296</v>
       </c>
       <c r="G347">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="H347">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="I347">
         <v>0</v>
@@ -10608,16 +10608,16 @@
         <v>266</v>
       </c>
       <c r="E352">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F352">
         <v>124</v>
       </c>
       <c r="G352">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H352">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I352">
         <v>0</v>
@@ -10666,16 +10666,16 @@
         <v>268</v>
       </c>
       <c r="E354">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F354">
         <v>212</v>
       </c>
       <c r="G354">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="H354">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I354">
         <v>0</v>
@@ -10956,16 +10956,16 @@
         <v>302</v>
       </c>
       <c r="E364">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F364">
         <v>100</v>
       </c>
       <c r="G364">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H364">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I364">
         <v>0</v>
@@ -10985,16 +10985,16 @@
         <v>303</v>
       </c>
       <c r="E365">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F365">
         <v>128</v>
       </c>
       <c r="G365">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="H365">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I365">
         <v>0</v>
@@ -11014,16 +11014,16 @@
         <v>304</v>
       </c>
       <c r="E366">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F366">
         <v>128</v>
       </c>
       <c r="G366">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="H366">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I366">
         <v>0</v>
@@ -11072,16 +11072,16 @@
         <v>569</v>
       </c>
       <c r="E368">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F368">
         <v>200</v>
       </c>
       <c r="G368">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="H368">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I368">
         <v>0</v>
@@ -11194,7 +11194,7 @@
         <v>280</v>
       </c>
       <c r="G372">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="H372">
         <v>0</v>
@@ -11275,16 +11275,16 @@
         <v>364</v>
       </c>
       <c r="E375">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F375">
         <v>40</v>
       </c>
       <c r="G375">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H375">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I375">
         <v>0</v>
@@ -11304,16 +11304,16 @@
         <v>365</v>
       </c>
       <c r="E376">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F376">
         <v>40</v>
       </c>
       <c r="G376">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H376">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I376">
         <v>0</v>
@@ -11449,16 +11449,16 @@
         <v>370</v>
       </c>
       <c r="E381">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F381">
         <v>32</v>
       </c>
       <c r="G381">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H381">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I381">
         <v>0</v>
@@ -11623,16 +11623,16 @@
         <v>376</v>
       </c>
       <c r="E387">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F387">
         <v>52</v>
       </c>
       <c r="G387">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="H387">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I387">
         <v>0</v>
@@ -11652,16 +11652,16 @@
         <v>377</v>
       </c>
       <c r="E388">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F388">
         <v>52</v>
       </c>
       <c r="G388">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="H388">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I388">
         <v>0</v>
@@ -11797,16 +11797,16 @@
         <v>382</v>
       </c>
       <c r="E393">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F393">
         <v>40</v>
       </c>
       <c r="G393">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H393">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I393">
         <v>0</v>
@@ -11826,16 +11826,16 @@
         <v>383</v>
       </c>
       <c r="E394">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F394">
         <v>40</v>
       </c>
       <c r="G394">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H394">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I394">
         <v>0</v>
@@ -12029,16 +12029,16 @@
         <v>390</v>
       </c>
       <c r="E401">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F401">
         <v>48</v>
       </c>
       <c r="G401">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="H401">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I401">
         <v>0</v>
@@ -12058,16 +12058,16 @@
         <v>391</v>
       </c>
       <c r="E402">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F402">
         <v>36</v>
       </c>
       <c r="G402">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H402">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I402">
         <v>0</v>
@@ -12145,16 +12145,16 @@
         <v>396</v>
       </c>
       <c r="E405">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F405">
         <v>40</v>
       </c>
       <c r="G405">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H405">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I405">
         <v>0</v>
@@ -12174,16 +12174,16 @@
         <v>397</v>
       </c>
       <c r="E406">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F406">
         <v>40</v>
       </c>
       <c r="G406">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H406">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I406">
         <v>0</v>
@@ -16836,7 +16836,7 @@
         <v>106</v>
       </c>
       <c r="E14">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F14">
         <v>76</v>
@@ -16848,7 +16848,7 @@
         <v>76</v>
       </c>
       <c r="I14">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15">
@@ -16865,7 +16865,7 @@
         <v>107</v>
       </c>
       <c r="E15">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F15">
         <v>60</v>
@@ -16877,7 +16877,7 @@
         <v>60</v>
       </c>
       <c r="I15">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16">
@@ -16894,7 +16894,7 @@
         <v>108</v>
       </c>
       <c r="E16">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F16">
         <v>68</v>
@@ -16906,7 +16906,7 @@
         <v>68</v>
       </c>
       <c r="I16">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17">
@@ -17068,7 +17068,7 @@
         <v>96</v>
       </c>
       <c r="E22">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="F22">
         <v>52</v>
@@ -17080,7 +17080,7 @@
         <v>52</v>
       </c>
       <c r="I22">
-        <v>136</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23">
@@ -17184,16 +17184,16 @@
         <v>148</v>
       </c>
       <c r="E26">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F26">
         <v>152</v>
       </c>
       <c r="G26">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H26">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -17213,16 +17213,16 @@
         <v>149</v>
       </c>
       <c r="E27">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F27">
         <v>136</v>
       </c>
       <c r="G27">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H27">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -17271,7 +17271,7 @@
         <v>151</v>
       </c>
       <c r="E29">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F29">
         <v>180</v>
@@ -17283,7 +17283,7 @@
         <v>180</v>
       </c>
       <c r="I29">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -18112,7 +18112,7 @@
         <v>76</v>
       </c>
       <c r="E58">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="F58">
         <v>204</v>
@@ -18124,7 +18124,7 @@
         <v>204</v>
       </c>
       <c r="I58">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
@@ -18141,19 +18141,19 @@
         <v>77</v>
       </c>
       <c r="E59">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="F59">
         <v>200</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I59">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -18170,16 +18170,16 @@
         <v>78</v>
       </c>
       <c r="E60">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F60">
         <v>184</v>
       </c>
       <c r="G60">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="H60">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -18373,7 +18373,7 @@
         <v>159</v>
       </c>
       <c r="E67">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F67">
         <v>116</v>
@@ -18385,7 +18385,7 @@
         <v>116</v>
       </c>
       <c r="I67">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68">
@@ -18402,16 +18402,16 @@
         <v>160</v>
       </c>
       <c r="E68">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="F68">
         <v>228</v>
       </c>
       <c r="G68">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="H68">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -18431,19 +18431,19 @@
         <v>161</v>
       </c>
       <c r="E69">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="F69">
         <v>204</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H69">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="I69">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -18460,7 +18460,7 @@
         <v>112</v>
       </c>
       <c r="E70">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F70">
         <v>144</v>
@@ -18472,7 +18472,7 @@
         <v>144</v>
       </c>
       <c r="I70">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="71">
@@ -18489,7 +18489,7 @@
         <v>113</v>
       </c>
       <c r="E71">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F71">
         <v>148</v>
@@ -18501,7 +18501,7 @@
         <v>148</v>
       </c>
       <c r="I71">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="72">
@@ -18518,7 +18518,7 @@
         <v>114</v>
       </c>
       <c r="E72">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F72">
         <v>84</v>
@@ -18530,7 +18530,7 @@
         <v>84</v>
       </c>
       <c r="I72">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="73">
@@ -18547,7 +18547,7 @@
         <v>103</v>
       </c>
       <c r="E73">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F73">
         <v>52</v>
@@ -18559,7 +18559,7 @@
         <v>52</v>
       </c>
       <c r="I73">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="74">
@@ -18605,7 +18605,7 @@
         <v>105</v>
       </c>
       <c r="E75">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F75">
         <v>64</v>
@@ -18617,7 +18617,7 @@
         <v>64</v>
       </c>
       <c r="I75">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="76">
@@ -18692,7 +18692,7 @@
         <v>144</v>
       </c>
       <c r="E78">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="F78">
         <v>100</v>
@@ -18704,7 +18704,7 @@
         <v>100</v>
       </c>
       <c r="I78">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="79">
@@ -18721,16 +18721,16 @@
         <v>185</v>
       </c>
       <c r="E79">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F79">
         <v>244</v>
       </c>
       <c r="G79">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H79">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -18750,7 +18750,7 @@
         <v>186</v>
       </c>
       <c r="E80">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="F80">
         <v>176</v>
@@ -18762,7 +18762,7 @@
         <v>176</v>
       </c>
       <c r="I80">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81">
@@ -18779,7 +18779,7 @@
         <v>187</v>
       </c>
       <c r="E81">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F81">
         <v>164</v>
@@ -18791,7 +18791,7 @@
         <v>164</v>
       </c>
       <c r="I81">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="82">
@@ -18808,7 +18808,7 @@
         <v>197</v>
       </c>
       <c r="E82">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F82">
         <v>68</v>
@@ -18820,7 +18820,7 @@
         <v>68</v>
       </c>
       <c r="I82">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="83">
@@ -18837,7 +18837,7 @@
         <v>198</v>
       </c>
       <c r="E83">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F83">
         <v>88</v>
@@ -18849,7 +18849,7 @@
         <v>88</v>
       </c>
       <c r="I83">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="84">
@@ -18866,7 +18866,7 @@
         <v>199</v>
       </c>
       <c r="E84">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F84">
         <v>64</v>
@@ -18878,7 +18878,7 @@
         <v>64</v>
       </c>
       <c r="I84">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="85">
@@ -18895,7 +18895,7 @@
         <v>194</v>
       </c>
       <c r="E85">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F85">
         <v>132</v>
@@ -18907,7 +18907,7 @@
         <v>132</v>
       </c>
       <c r="I85">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="86">
@@ -18924,7 +18924,7 @@
         <v>195</v>
       </c>
       <c r="E86">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F86">
         <v>124</v>
@@ -18936,7 +18936,7 @@
         <v>124</v>
       </c>
       <c r="I86">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="87">
@@ -18953,7 +18953,7 @@
         <v>196</v>
       </c>
       <c r="E87">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F87">
         <v>120</v>
@@ -18965,7 +18965,7 @@
         <v>120</v>
       </c>
       <c r="I87">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="88">
@@ -18982,7 +18982,7 @@
         <v>200</v>
       </c>
       <c r="E88">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="F88">
         <v>156</v>
@@ -18994,7 +18994,7 @@
         <v>156</v>
       </c>
       <c r="I88">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="89">
@@ -19011,16 +19011,16 @@
         <v>201</v>
       </c>
       <c r="E89">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F89">
         <v>196</v>
       </c>
       <c r="G89">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H89">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -19069,16 +19069,16 @@
         <v>305</v>
       </c>
       <c r="E91">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F91">
         <v>200</v>
       </c>
       <c r="G91">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H91">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -19098,16 +19098,16 @@
         <v>306</v>
       </c>
       <c r="E92">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F92">
         <v>144</v>
       </c>
       <c r="G92">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H92">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -19127,16 +19127,16 @@
         <v>307</v>
       </c>
       <c r="E93">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F93">
         <v>104</v>
       </c>
       <c r="G93">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H93">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -19156,7 +19156,7 @@
         <v>308</v>
       </c>
       <c r="E94">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F94">
         <v>80</v>
@@ -19168,7 +19168,7 @@
         <v>80</v>
       </c>
       <c r="I94">
-        <v>67</v>
+        <v>48</v>
       </c>
     </row>
     <row r="95">
@@ -19214,7 +19214,7 @@
         <v>310</v>
       </c>
       <c r="E96">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="F96">
         <v>60</v>
@@ -19226,7 +19226,7 @@
         <v>60</v>
       </c>
       <c r="I96">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="97">
@@ -19243,7 +19243,7 @@
         <v>311</v>
       </c>
       <c r="E97">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="F97">
         <v>56</v>
@@ -19255,7 +19255,7 @@
         <v>56</v>
       </c>
       <c r="I97">
-        <v>73</v>
+        <v>60</v>
       </c>
     </row>
     <row r="98">
@@ -19272,16 +19272,16 @@
         <v>312</v>
       </c>
       <c r="E98">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F98">
         <v>224</v>
       </c>
       <c r="G98">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H98">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -19301,16 +19301,16 @@
         <v>313</v>
       </c>
       <c r="E99">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F99">
         <v>304</v>
       </c>
       <c r="G99">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="H99">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -19330,16 +19330,16 @@
         <v>314</v>
       </c>
       <c r="E100">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F100">
         <v>208</v>
       </c>
       <c r="G100">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H100">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -19388,16 +19388,16 @@
         <v>316</v>
       </c>
       <c r="E102">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F102">
         <v>216</v>
       </c>
       <c r="G102">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H102">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I102">
         <v>0</v>
@@ -19417,16 +19417,16 @@
         <v>317</v>
       </c>
       <c r="E103">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F103">
         <v>204</v>
       </c>
       <c r="G103">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="H103">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I103">
         <v>0</v>
@@ -19446,16 +19446,16 @@
         <v>318</v>
       </c>
       <c r="E104">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F104">
         <v>164</v>
       </c>
       <c r="G104">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="H104">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I104">
         <v>0</v>
@@ -19475,16 +19475,16 @@
         <v>319</v>
       </c>
       <c r="E105">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F105">
         <v>148</v>
       </c>
       <c r="G105">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="H105">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -19533,16 +19533,16 @@
         <v>321</v>
       </c>
       <c r="E107">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F107">
         <v>176</v>
       </c>
       <c r="G107">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="H107">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I107">
         <v>0</v>
@@ -19562,16 +19562,16 @@
         <v>322</v>
       </c>
       <c r="E108">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F108">
         <v>124</v>
       </c>
       <c r="G108">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="H108">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -19591,16 +19591,16 @@
         <v>323</v>
       </c>
       <c r="E109">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F109">
         <v>184</v>
       </c>
       <c r="G109">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="H109">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I109">
         <v>0</v>
@@ -19707,16 +19707,16 @@
         <v>327</v>
       </c>
       <c r="E113">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F113">
         <v>100</v>
       </c>
       <c r="G113">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H113">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I113">
         <v>0</v>
@@ -19794,16 +19794,16 @@
         <v>330</v>
       </c>
       <c r="E116">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F116">
         <v>72</v>
       </c>
       <c r="G116">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="H116">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I116">
         <v>0</v>
@@ -19823,16 +19823,16 @@
         <v>331</v>
       </c>
       <c r="E117">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F117">
         <v>84</v>
       </c>
       <c r="G117">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H117">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I117">
         <v>0</v>
@@ -19852,16 +19852,16 @@
         <v>332</v>
       </c>
       <c r="E118">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F118">
         <v>108</v>
       </c>
       <c r="G118">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="H118">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I118">
         <v>0</v>
@@ -19881,16 +19881,16 @@
         <v>547</v>
       </c>
       <c r="E119">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F119">
         <v>72</v>
       </c>
       <c r="G119">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H119">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I119">
         <v>0</v>
@@ -19910,16 +19910,16 @@
         <v>548</v>
       </c>
       <c r="E120">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F120">
         <v>64</v>
       </c>
       <c r="G120">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H120">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I120">
         <v>0</v>
@@ -19939,16 +19939,16 @@
         <v>549</v>
       </c>
       <c r="E121">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F121">
         <v>76</v>
       </c>
       <c r="G121">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H121">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I121">
         <v>0</v>
@@ -20084,7 +20084,7 @@
         <v>85</v>
       </c>
       <c r="E126">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F126">
         <v>148</v>
@@ -20096,7 +20096,7 @@
         <v>148</v>
       </c>
       <c r="I126">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="127">
@@ -20113,7 +20113,7 @@
         <v>86</v>
       </c>
       <c r="E127">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="F127">
         <v>128</v>
@@ -20125,7 +20125,7 @@
         <v>128</v>
       </c>
       <c r="I127">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="128">
@@ -20142,7 +20142,7 @@
         <v>87</v>
       </c>
       <c r="E128">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F128">
         <v>84</v>
@@ -20154,7 +20154,7 @@
         <v>84</v>
       </c>
       <c r="I128">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="129">
@@ -20345,7 +20345,7 @@
         <v>230</v>
       </c>
       <c r="E135">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F135">
         <v>60</v>
@@ -20357,7 +20357,7 @@
         <v>60</v>
       </c>
       <c r="I135">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="136">
@@ -20432,7 +20432,7 @@
         <v>115</v>
       </c>
       <c r="E138">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F138">
         <v>48</v>
@@ -20444,7 +20444,7 @@
         <v>48</v>
       </c>
       <c r="I138">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="139">
@@ -20490,7 +20490,7 @@
         <v>117</v>
       </c>
       <c r="E140">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F140">
         <v>64</v>
@@ -20502,7 +20502,7 @@
         <v>64</v>
       </c>
       <c r="I140">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="141">
@@ -20606,7 +20606,7 @@
         <v>145</v>
       </c>
       <c r="E144">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="F144">
         <v>124</v>
@@ -20618,7 +20618,7 @@
         <v>124</v>
       </c>
       <c r="I144">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="145">
@@ -20664,7 +20664,7 @@
         <v>147</v>
       </c>
       <c r="E146">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F146">
         <v>132</v>
@@ -20676,7 +20676,7 @@
         <v>132</v>
       </c>
       <c r="I146">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="147">
@@ -20693,7 +20693,7 @@
         <v>182</v>
       </c>
       <c r="E147">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F147">
         <v>172</v>
@@ -20705,7 +20705,7 @@
         <v>172</v>
       </c>
       <c r="I147">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="148">
@@ -20780,7 +20780,7 @@
         <v>203</v>
       </c>
       <c r="E150">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F150">
         <v>52</v>
@@ -20792,7 +20792,7 @@
         <v>52</v>
       </c>
       <c r="I150">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="151">
@@ -20867,7 +20867,7 @@
         <v>206</v>
       </c>
       <c r="E153">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F153">
         <v>92</v>
@@ -20879,7 +20879,7 @@
         <v>92</v>
       </c>
       <c r="I153">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="154">
@@ -20954,7 +20954,7 @@
         <v>209</v>
       </c>
       <c r="E156">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="F156">
         <v>156</v>
@@ -20966,7 +20966,7 @@
         <v>156</v>
       </c>
       <c r="I156">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="157">
@@ -21128,7 +21128,7 @@
         <v>336</v>
       </c>
       <c r="E162">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F162">
         <v>92</v>
@@ -21140,7 +21140,7 @@
         <v>92</v>
       </c>
       <c r="I162">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="163">
@@ -21157,7 +21157,7 @@
         <v>337</v>
       </c>
       <c r="E163">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="F163">
         <v>104</v>
@@ -21169,7 +21169,7 @@
         <v>104</v>
       </c>
       <c r="I163">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="164">
@@ -21186,7 +21186,7 @@
         <v>338</v>
       </c>
       <c r="E164">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F164">
         <v>132</v>
@@ -21198,7 +21198,7 @@
         <v>132</v>
       </c>
       <c r="I164">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="165">
@@ -21215,16 +21215,16 @@
         <v>339</v>
       </c>
       <c r="E165">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F165">
         <v>272</v>
       </c>
       <c r="G165">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="H165">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I165">
         <v>0</v>
@@ -21273,16 +21273,16 @@
         <v>341</v>
       </c>
       <c r="E167">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F167">
         <v>272</v>
       </c>
       <c r="G167">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="H167">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I167">
         <v>0</v>
@@ -21302,16 +21302,16 @@
         <v>342</v>
       </c>
       <c r="E168">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F168">
         <v>216</v>
       </c>
       <c r="G168">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H168">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I168">
         <v>0</v>
@@ -21360,16 +21360,16 @@
         <v>344</v>
       </c>
       <c r="E170">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F170">
         <v>224</v>
       </c>
       <c r="G170">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="H170">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I170">
         <v>0</v>
@@ -21389,16 +21389,16 @@
         <v>345</v>
       </c>
       <c r="E171">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F171">
         <v>100</v>
       </c>
       <c r="G171">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H171">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I171">
         <v>0</v>
@@ -21418,16 +21418,16 @@
         <v>346</v>
       </c>
       <c r="E172">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F172">
         <v>132</v>
       </c>
       <c r="G172">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H172">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I172">
         <v>0</v>
@@ -21447,16 +21447,16 @@
         <v>347</v>
       </c>
       <c r="E173">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F173">
         <v>120</v>
       </c>
       <c r="G173">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H173">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I173">
         <v>0</v>
@@ -21476,16 +21476,16 @@
         <v>351</v>
       </c>
       <c r="E174">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F174">
         <v>140</v>
       </c>
       <c r="G174">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H174">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I174">
         <v>0</v>
@@ -21534,16 +21534,16 @@
         <v>353</v>
       </c>
       <c r="E176">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F176">
         <v>176</v>
       </c>
       <c r="G176">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="H176">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I176">
         <v>0</v>
@@ -21737,16 +21737,16 @@
         <v>357</v>
       </c>
       <c r="E183">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F183">
         <v>132</v>
       </c>
       <c r="G183">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H183">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I183">
         <v>0</v>
@@ -21766,16 +21766,16 @@
         <v>358</v>
       </c>
       <c r="E184">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F184">
         <v>136</v>
       </c>
       <c r="G184">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H184">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I184">
         <v>0</v>
@@ -21795,16 +21795,16 @@
         <v>359</v>
       </c>
       <c r="E185">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F185">
         <v>152</v>
       </c>
       <c r="G185">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H185">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I185">
         <v>0</v>
@@ -22049,7 +22049,7 @@
         <v>67</v>
       </c>
       <c r="E5">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F5">
         <v>148</v>
@@ -22061,7 +22061,7 @@
         <v>148</v>
       </c>
       <c r="I5">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
@@ -22078,7 +22078,7 @@
         <v>68</v>
       </c>
       <c r="E6">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F6">
         <v>188</v>
@@ -22090,7 +22090,7 @@
         <v>188</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -22107,7 +22107,7 @@
         <v>69</v>
       </c>
       <c r="E7">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F7">
         <v>136</v>
@@ -22119,7 +22119,7 @@
         <v>136</v>
       </c>
       <c r="I7">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
@@ -22136,7 +22136,7 @@
         <v>70</v>
       </c>
       <c r="E8">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F8">
         <v>148</v>
@@ -22148,7 +22148,7 @@
         <v>148</v>
       </c>
       <c r="I8">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9">
@@ -22165,7 +22165,7 @@
         <v>71</v>
       </c>
       <c r="E9">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F9">
         <v>160</v>
@@ -22177,7 +22177,7 @@
         <v>160</v>
       </c>
       <c r="I9">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -22223,7 +22223,7 @@
         <v>73</v>
       </c>
       <c r="E11">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F11">
         <v>108</v>
@@ -22235,7 +22235,7 @@
         <v>108</v>
       </c>
       <c r="I11">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -22252,7 +22252,7 @@
         <v>74</v>
       </c>
       <c r="E12">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F12">
         <v>96</v>
@@ -22264,7 +22264,7 @@
         <v>96</v>
       </c>
       <c r="I12">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13">
@@ -22600,7 +22600,7 @@
         <v>179</v>
       </c>
       <c r="E24">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F24">
         <v>136</v>
@@ -22612,7 +22612,7 @@
         <v>136</v>
       </c>
       <c r="I24">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25">
@@ -22629,16 +22629,16 @@
         <v>180</v>
       </c>
       <c r="E25">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F25">
         <v>136</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H25">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -22658,16 +22658,16 @@
         <v>181</v>
       </c>
       <c r="E26">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F26">
         <v>100</v>
       </c>
       <c r="G26">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H26">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -22687,7 +22687,7 @@
         <v>212</v>
       </c>
       <c r="E27">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F27">
         <v>80</v>
@@ -22699,7 +22699,7 @@
         <v>80</v>
       </c>
       <c r="I27">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28">
@@ -22774,7 +22774,7 @@
         <v>215</v>
       </c>
       <c r="E30">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F30">
         <v>40</v>
@@ -22786,7 +22786,7 @@
         <v>40</v>
       </c>
       <c r="I30">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31">
@@ -23122,16 +23122,16 @@
         <v>281</v>
       </c>
       <c r="E42">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F42">
         <v>168</v>
       </c>
       <c r="G42">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H42">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -23151,16 +23151,16 @@
         <v>282</v>
       </c>
       <c r="E43">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F43">
         <v>236</v>
       </c>
       <c r="G43">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="H43">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -23180,16 +23180,16 @@
         <v>283</v>
       </c>
       <c r="E44">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F44">
         <v>212</v>
       </c>
       <c r="G44">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H44">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -23296,16 +23296,16 @@
         <v>556</v>
       </c>
       <c r="E48">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F48">
         <v>144</v>
       </c>
       <c r="G48">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H48">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -23325,16 +23325,16 @@
         <v>557</v>
       </c>
       <c r="E49">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F49">
         <v>260</v>
       </c>
       <c r="G49">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="H49">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -23586,7 +23586,7 @@
         <v>12</v>
       </c>
       <c r="E58">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="F58">
         <v>112</v>
@@ -23598,7 +23598,7 @@
         <v>112</v>
       </c>
       <c r="I58">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59">
@@ -23615,7 +23615,7 @@
         <v>13</v>
       </c>
       <c r="E59">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F59">
         <v>152</v>
@@ -23627,7 +23627,7 @@
         <v>152</v>
       </c>
       <c r="I59">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="60">
@@ -23644,7 +23644,7 @@
         <v>14</v>
       </c>
       <c r="E60">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="F60">
         <v>92</v>
@@ -23656,7 +23656,7 @@
         <v>92</v>
       </c>
       <c r="I60">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61">
@@ -23702,7 +23702,7 @@
         <v>41</v>
       </c>
       <c r="E62">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="F62">
         <v>172</v>
@@ -23714,7 +23714,7 @@
         <v>172</v>
       </c>
       <c r="I62">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63">
@@ -23731,7 +23731,7 @@
         <v>42</v>
       </c>
       <c r="E63">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="F63">
         <v>136</v>
@@ -23743,7 +23743,7 @@
         <v>136</v>
       </c>
       <c r="I63">
-        <v>73</v>
+        <v>63</v>
       </c>
     </row>
     <row r="64">
@@ -23760,16 +23760,16 @@
         <v>55</v>
       </c>
       <c r="E64">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F64">
         <v>212</v>
       </c>
       <c r="G64">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H64">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -23905,7 +23905,7 @@
         <v>54</v>
       </c>
       <c r="E69">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="F69">
         <v>108</v>
@@ -23917,7 +23917,7 @@
         <v>108</v>
       </c>
       <c r="I69">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="70">
@@ -23934,16 +23934,16 @@
         <v>124</v>
       </c>
       <c r="E70">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F70">
         <v>276</v>
       </c>
       <c r="G70">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H70">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -23992,16 +23992,16 @@
         <v>126</v>
       </c>
       <c r="E72">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F72">
         <v>248</v>
       </c>
       <c r="G72">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="H72">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -24108,7 +24108,7 @@
         <v>136</v>
       </c>
       <c r="E76">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F76">
         <v>104</v>
@@ -24120,7 +24120,7 @@
         <v>104</v>
       </c>
       <c r="I76">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="77">
@@ -24137,7 +24137,7 @@
         <v>137</v>
       </c>
       <c r="E77">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F77">
         <v>152</v>
@@ -24149,7 +24149,7 @@
         <v>152</v>
       </c>
       <c r="I77">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="78">
@@ -24166,7 +24166,7 @@
         <v>138</v>
       </c>
       <c r="E78">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F78">
         <v>104</v>
@@ -24178,7 +24178,7 @@
         <v>104</v>
       </c>
       <c r="I78">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="79">
@@ -24195,16 +24195,16 @@
         <v>139</v>
       </c>
       <c r="E79">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="F79">
         <v>228</v>
       </c>
       <c r="G79">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H79">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -24224,7 +24224,7 @@
         <v>140</v>
       </c>
       <c r="E80">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F80">
         <v>140</v>
@@ -24236,7 +24236,7 @@
         <v>140</v>
       </c>
       <c r="I80">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="81">
@@ -24253,7 +24253,7 @@
         <v>141</v>
       </c>
       <c r="E81">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="F81">
         <v>172</v>
@@ -24265,7 +24265,7 @@
         <v>172</v>
       </c>
       <c r="I81">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="82">
@@ -24282,16 +24282,16 @@
         <v>169</v>
       </c>
       <c r="E82">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F82">
         <v>216</v>
       </c>
       <c r="G82">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H82">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -24340,16 +24340,16 @@
         <v>171</v>
       </c>
       <c r="E84">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F84">
         <v>204</v>
       </c>
       <c r="G84">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H84">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -24369,7 +24369,7 @@
         <v>218</v>
       </c>
       <c r="E85">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="F85">
         <v>168</v>
@@ -24381,7 +24381,7 @@
         <v>168</v>
       </c>
       <c r="I85">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86">
@@ -24398,7 +24398,7 @@
         <v>219</v>
       </c>
       <c r="E86">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="F86">
         <v>172</v>
@@ -24410,7 +24410,7 @@
         <v>172</v>
       </c>
       <c r="I86">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87">
@@ -24427,7 +24427,7 @@
         <v>220</v>
       </c>
       <c r="E87">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="F87">
         <v>100</v>
@@ -24439,7 +24439,7 @@
         <v>100</v>
       </c>
       <c r="I87">
-        <v>74</v>
+        <v>64</v>
       </c>
     </row>
     <row r="88">
@@ -24456,7 +24456,7 @@
         <v>221</v>
       </c>
       <c r="E88">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F88">
         <v>56</v>
@@ -24468,7 +24468,7 @@
         <v>56</v>
       </c>
       <c r="I88">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="89">
@@ -24485,7 +24485,7 @@
         <v>222</v>
       </c>
       <c r="E89">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F89">
         <v>124</v>
@@ -24497,7 +24497,7 @@
         <v>124</v>
       </c>
       <c r="I89">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="90">
@@ -24543,16 +24543,16 @@
         <v>248</v>
       </c>
       <c r="E91">
-        <v>358</v>
+        <v>172</v>
       </c>
       <c r="F91">
         <v>372</v>
       </c>
       <c r="G91">
-        <v>14</v>
+        <v>200</v>
       </c>
       <c r="H91">
-        <v>358</v>
+        <v>172</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -24572,16 +24572,16 @@
         <v>249</v>
       </c>
       <c r="E92">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="F92">
         <v>228</v>
       </c>
       <c r="G92">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H92">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -24601,16 +24601,16 @@
         <v>250</v>
       </c>
       <c r="E93">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="F93">
         <v>368</v>
       </c>
       <c r="G93">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="H93">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -24630,7 +24630,7 @@
         <v>251</v>
       </c>
       <c r="E94">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F94">
         <v>52</v>
@@ -24642,7 +24642,7 @@
         <v>52</v>
       </c>
       <c r="I94">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="95">
@@ -24659,7 +24659,7 @@
         <v>252</v>
       </c>
       <c r="E95">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F95">
         <v>52</v>
@@ -24671,7 +24671,7 @@
         <v>52</v>
       </c>
       <c r="I95">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="96">
@@ -24688,7 +24688,7 @@
         <v>253</v>
       </c>
       <c r="E96">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F96">
         <v>68</v>
@@ -24700,7 +24700,7 @@
         <v>68</v>
       </c>
       <c r="I96">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="97">
@@ -24746,16 +24746,16 @@
         <v>255</v>
       </c>
       <c r="E98">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F98">
         <v>160</v>
       </c>
       <c r="G98">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="H98">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -24775,16 +24775,16 @@
         <v>256</v>
       </c>
       <c r="E99">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F99">
         <v>108</v>
       </c>
       <c r="G99">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H99">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -24978,16 +24978,16 @@
         <v>293</v>
       </c>
       <c r="E106">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F106">
         <v>172</v>
       </c>
       <c r="G106">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="H106">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I106">
         <v>0</v>
@@ -25036,16 +25036,16 @@
         <v>295</v>
       </c>
       <c r="E108">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F108">
         <v>196</v>
       </c>
       <c r="G108">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="H108">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -25065,16 +25065,16 @@
         <v>296</v>
       </c>
       <c r="E109">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F109">
         <v>192</v>
       </c>
       <c r="G109">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="H109">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I109">
         <v>0</v>
@@ -25094,16 +25094,16 @@
         <v>297</v>
       </c>
       <c r="E110">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F110">
         <v>132</v>
       </c>
       <c r="G110">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H110">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I110">
         <v>0</v>
@@ -25123,16 +25123,16 @@
         <v>298</v>
       </c>
       <c r="E111">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F111">
         <v>192</v>
       </c>
       <c r="G111">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="H111">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I111">
         <v>0</v>
@@ -25239,16 +25239,16 @@
         <v>565</v>
       </c>
       <c r="E115">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F115">
         <v>140</v>
       </c>
       <c r="G115">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H115">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I115">
         <v>0</v>
@@ -25268,16 +25268,16 @@
         <v>566</v>
       </c>
       <c r="E116">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F116">
         <v>220</v>
       </c>
       <c r="G116">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H116">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I116">
         <v>0</v>
@@ -25297,16 +25297,16 @@
         <v>567</v>
       </c>
       <c r="E117">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F117">
         <v>192</v>
       </c>
       <c r="G117">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H117">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I117">
         <v>0</v>
@@ -25500,16 +25500,16 @@
         <v>18</v>
       </c>
       <c r="E124">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F124">
         <v>212</v>
       </c>
       <c r="G124">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="H124">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="I124">
         <v>0</v>
@@ -26254,7 +26254,7 @@
         <v>166</v>
       </c>
       <c r="E150">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F150">
         <v>56</v>
@@ -26266,7 +26266,7 @@
         <v>56</v>
       </c>
       <c r="I150">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="151">
@@ -26312,7 +26312,7 @@
         <v>168</v>
       </c>
       <c r="E152">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F152">
         <v>120</v>
@@ -26324,7 +26324,7 @@
         <v>120</v>
       </c>
       <c r="I152">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="153">
@@ -26370,16 +26370,16 @@
         <v>225</v>
       </c>
       <c r="E154">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F154">
         <v>112</v>
       </c>
       <c r="G154">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H154">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I154">
         <v>0</v>
@@ -26399,7 +26399,7 @@
         <v>226</v>
       </c>
       <c r="E155">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F155">
         <v>164</v>
@@ -26411,7 +26411,7 @@
         <v>164</v>
       </c>
       <c r="I155">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="156">
@@ -26428,7 +26428,7 @@
         <v>227</v>
       </c>
       <c r="E156">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F156">
         <v>68</v>
@@ -26440,7 +26440,7 @@
         <v>68</v>
       </c>
       <c r="I156">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="157">
@@ -26486,7 +26486,7 @@
         <v>229</v>
       </c>
       <c r="E158">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F158">
         <v>120</v>
@@ -26498,7 +26498,7 @@
         <v>120</v>
       </c>
       <c r="I158">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="159">
@@ -26515,16 +26515,16 @@
         <v>260</v>
       </c>
       <c r="E159">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="F159">
         <v>324</v>
       </c>
       <c r="G159">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H159">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="I159">
         <v>0</v>
@@ -26544,16 +26544,16 @@
         <v>261</v>
       </c>
       <c r="E160">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="F160">
         <v>296</v>
       </c>
       <c r="G160">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="H160">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="I160">
         <v>0</v>
@@ -26689,16 +26689,16 @@
         <v>266</v>
       </c>
       <c r="E165">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F165">
         <v>124</v>
       </c>
       <c r="G165">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H165">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I165">
         <v>0</v>
@@ -26747,16 +26747,16 @@
         <v>268</v>
       </c>
       <c r="E167">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F167">
         <v>212</v>
       </c>
       <c r="G167">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="H167">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I167">
         <v>0</v>
@@ -27037,16 +27037,16 @@
         <v>302</v>
       </c>
       <c r="E177">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F177">
         <v>100</v>
       </c>
       <c r="G177">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H177">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I177">
         <v>0</v>
@@ -27066,16 +27066,16 @@
         <v>303</v>
       </c>
       <c r="E178">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F178">
         <v>128</v>
       </c>
       <c r="G178">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="H178">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I178">
         <v>0</v>
@@ -27095,16 +27095,16 @@
         <v>304</v>
       </c>
       <c r="E179">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F179">
         <v>128</v>
       </c>
       <c r="G179">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="H179">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I179">
         <v>0</v>
@@ -27153,16 +27153,16 @@
         <v>569</v>
       </c>
       <c r="E181">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F181">
         <v>200</v>
       </c>
       <c r="G181">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="H181">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I181">
         <v>0</v>
@@ -27275,7 +27275,7 @@
         <v>280</v>
       </c>
       <c r="G185">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="H185">
         <v>0</v>
@@ -27407,16 +27407,16 @@
         <v>364</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>40</v>
       </c>
       <c r="G4">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -27436,16 +27436,16 @@
         <v>365</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>40</v>
       </c>
       <c r="G5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -27581,16 +27581,16 @@
         <v>370</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F10">
         <v>32</v>
       </c>
       <c r="G10">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H10">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -27755,16 +27755,16 @@
         <v>376</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>52</v>
       </c>
       <c r="G16">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="H16">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -27784,16 +27784,16 @@
         <v>377</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>52</v>
       </c>
       <c r="G17">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="H17">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -27929,16 +27929,16 @@
         <v>382</v>
       </c>
       <c r="E22">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>40</v>
       </c>
       <c r="G22">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H22">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -27958,16 +27958,16 @@
         <v>383</v>
       </c>
       <c r="E23">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>40</v>
       </c>
       <c r="G23">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H23">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -28161,16 +28161,16 @@
         <v>390</v>
       </c>
       <c r="E30">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F30">
         <v>48</v>
       </c>
       <c r="G30">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="H30">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -28190,16 +28190,16 @@
         <v>391</v>
       </c>
       <c r="E31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F31">
         <v>36</v>
       </c>
       <c r="G31">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -28277,16 +28277,16 @@
         <v>396</v>
       </c>
       <c r="E34">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F34">
         <v>40</v>
       </c>
       <c r="G34">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H34">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -28306,16 +28306,16 @@
         <v>397</v>
       </c>
       <c r="E35">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F35">
         <v>40</v>
       </c>
       <c r="G35">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H35">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I35">
         <v>0</v>
